--- a/Planning/LAUNCH/Progress_Tees_Valley_Weekly_Plan_Week05_28Sep.xlsx
+++ b/Planning/LAUNCH/Progress_Tees_Valley_Weekly_Plan_Week05_28Sep.xlsx
@@ -1160,7 +1160,7 @@
     <row r="8" ht="45.75" customHeight="1" s="49">
       <c r="A8" s="57" t="inlineStr">
         <is>
-          <t>SMSC/BV this week: Black History Month launches (Thu 1 Oct, runs to W8) — Launch Humanities' migration unit carries it; PSHE's stereotype-and-respect thread supports.  National Poetry Day Thu 1 Oct (tbc).  EVIDENCE: display + EFL: cultural; log the BHM launch → log in the SMSC Evidence Tracker.</t>
+          <t>SMSC/BV this week: Black History Month launches (Thu 1 Oct, runs to W8) — Launch Humanities' migration unit carries it; PSHE's stereotype-and-respect thread supports.  National Poetry Day Thu 1 Oct (tbc).  EVIDENCE: display + evidence platform: cultural; log the BHM launch → log in the SMSC Evidence Tracker.</t>
         </is>
       </c>
       <c r="B8" s="58" t="n"/>
@@ -1471,7 +1471,7 @@
       <c r="I13" s="70" t="inlineStr">
         <is>
           <t>TA plays the 'pressurer' so pupils never pressure each other; teacher coaches the assertive version live; clips are the evidence.
-LOOP [Feedback Policy]: Voice = recorded micro-interview / script-flip / portfolio piece [VF] → Audience: listen fully, name one strength + one [NS] before tagging; then [R] → EVIDENCE: recording/portfolio to EFL, same day [E: PfA/careers/transition — weekly PfA minimum].</t>
+LOOP [Feedback Policy]: Voice = recorded micro-interview / script-flip / portfolio piece [VF] → Audience: listen fully, name one strength + one [NS] before tagging; then [R] → EVIDENCE: recording/portfolio to evidence platform, same day [E: PfA/careers/transition — weekly PfA minimum].</t>
         </is>
       </c>
       <c r="J13" s="70" t="inlineStr">
